--- a/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartProcessConfig@s.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartProcessConfig@s.xlsx
@@ -462,9 +462,15 @@
       </c>
     </row>
     <row r="7" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
+        <v>20002</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
